--- a/files/base-data-template.xlsx
+++ b/files/base-data-template.xlsx
@@ -402,9 +402,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A18"/>
-  <cols>
-    <col min="1" max="1" width="100.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -505,13 +502,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
-  <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="44.83203125" customWidth="1"/>
-    <col min="4" max="4" width="28.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:D37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -781,77 +772,77 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>입찰 공고일(제출 시작일)</v>
+        <v>입찰 공고번호</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>예: 2026-15 — 입찰 공고문·참가 신청서의 '공고 제○○호'</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-26</v>
+        <v>2026-15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>제출 시작 시각</v>
+        <v>입찰 공고일(제출 시작일)</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>예: 11:00</v>
+        <v/>
       </c>
       <c r="D21" t="str">
-        <v>10:00</v>
+        <v>2026-05-26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>제출 마감일</v>
+        <v>제출 시작 시각</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>견본품 기간 고려: 공고일~평가일 1개월 이상</v>
+        <v>예: 11:00</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-06-26</v>
+        <v>10:00</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>제출 마감 시각</v>
+        <v>제출 마감일</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>예: 14:00</v>
+        <v>견본품 기간 고려: 공고일~평가일 1개월 이상</v>
       </c>
       <c r="D23" t="str">
-        <v>14:00</v>
+        <v>2026-06-26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>제안서 평가일</v>
+        <v>제출 마감 시각</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>예: 14:00</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-06-29</v>
+        <v>14:00</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>제안서 평가 시각</v>
+        <v>제안서 평가일</v>
       </c>
       <c r="B25" t="str">
         <v/>
@@ -860,40 +851,40 @@
         <v/>
       </c>
       <c r="D25" t="str">
-        <v>15:30</v>
+        <v>2026-06-29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>제안서 평가 장소</v>
+        <v>제안서 평가 시각</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>예: ○○회의실</v>
+        <v/>
       </c>
       <c r="D26" t="str">
-        <v>○○회의실</v>
+        <v>15:30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>개찰일</v>
+        <v>제안서 평가 장소</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>예: ○○회의실</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-06-30</v>
+        <v>○○회의실</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>개찰 시각</v>
+        <v>개찰일</v>
       </c>
       <c r="B28" t="str">
         <v/>
@@ -902,82 +893,82 @@
         <v/>
       </c>
       <c r="D28" t="str">
-        <v>11:00</v>
+        <v>2026-06-30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>적격 기준 점수</v>
+        <v>개찰 시각</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>예: 80</v>
+        <v/>
       </c>
       <c r="D29" t="str">
-        <v>80</v>
+        <v>11:00</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>예정가격(단가)</v>
+        <v>적격 기준 점수</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>원</v>
+        <v>예: 80</v>
       </c>
       <c r="D30" t="str">
-        <v>337000</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>낙찰 업체명</v>
+        <v>예정가격(단가)</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>원</v>
       </c>
       <c r="D31" t="str">
-        <v>○○교복사</v>
+        <v>337000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>낙찰 업체 대표자</v>
+        <v>낙찰 업체명</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>비우면 아래 업체 목록에서 가져옵니다</v>
+        <v/>
       </c>
       <c r="D32" t="str">
-        <v/>
+        <v>○○교복사</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>낙찰 업체 소재지</v>
+        <v>낙찰 업체 대표자</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>비우면 아래 업체 목록에서 가져옵니다</v>
       </c>
       <c r="D33" t="str">
-        <v>전북특별자치도 ○○시 ○○로 00</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>낙찰 업체 전화</v>
+        <v>낙찰 업체 소재지</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -986,40 +977,54 @@
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>063-000-0000</v>
+        <v>전북특별자치도 ○○시 ○○로 00</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>투찰 단가</v>
+        <v>낙찰 업체 전화</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>원 — 계약금액 = 투찰 단가 × 구매 예정 인원</v>
+        <v/>
       </c>
       <c r="D35" t="str">
-        <v>301500</v>
+        <v>063-000-0000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
+        <v>투찰 단가</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v>원 — 계약금액 = 투찰 단가 × 구매 예정 인원</v>
+      </c>
+      <c r="D36" t="str">
+        <v>301500</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
         <v>계약 서류 제출기한</v>
       </c>
-      <c r="B36" t="str">
-        <v/>
-      </c>
-      <c r="C36" t="str">
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
         <v>낙찰 통지 후 10일 이내 계약</v>
       </c>
-      <c r="D36" t="str">
+      <c r="D37" t="str">
         <v>2026-07-08</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D37"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1027,12 +1032,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D10"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1184,16 +1183,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" customWidth="1"/>
-    <col min="6" max="6" width="9.83203125" customWidth="1"/>
-    <col min="7" max="7" width="9.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1361,11 +1350,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
